--- a/data/chart/input/old_chart_13/地瓜阁app商家提现周结.xlsx
+++ b/data/chart/input/old_chart_13/地瓜阁app商家提现周结.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangxin1/Desktop/datasets/数据分析/input/wps-1-2/可视化/old_chart_13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473C9EAA-FA14-ED43-B739-7A58468FD3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{473C9EAA-FA14-ED43-B739-7A58468FD3F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E579C85-8780-4109-943B-C9825B0362D6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,13 @@
     <sheet name="202408311720000550" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'202408311720000550'!$A$1:$G$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'202408311720000550'!$A$1:$F$41</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="192">
   <si>
     <t>序号</t>
   </si>
@@ -44,9 +47,6 @@
     <t>打款公式让对方客服填写</t>
   </si>
   <si>
-    <t>excel文件上传</t>
-  </si>
-  <si>
     <t>提现商家</t>
   </si>
   <si>
@@ -65,9 +65,6 @@
     <t>13459692494</t>
   </si>
   <si>
-    <t>和泰传媒有限公司</t>
-  </si>
-  <si>
     <t>yc</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
   </si>
   <si>
     <t>19591104592</t>
-  </si>
-  <si>
-    <t>迪摩信息有限公司</t>
   </si>
   <si>
     <t>2794.5</t>
@@ -158,9 +152,6 @@
 1369609043	270
 	-6
 	358462</t>
-  </si>
-  <si>
-    <t>盟新网络有限公司</t>
   </si>
   <si>
     <t>多游</t>
@@ -235,9 +226,6 @@
 		23914</t>
   </si>
   <si>
-    <t>凌颖信息网络有限公司</t>
-  </si>
-  <si>
     <t>极游</t>
   </si>
   <si>
@@ -268,9 +256,6 @@
 	9637</t>
   </si>
   <si>
-    <t>银嘉信息有限公司</t>
-  </si>
-  <si>
     <t>游星</t>
   </si>
   <si>
@@ -335,9 +320,6 @@
 3196961836	207
 3605611056	229.5
 	61237</t>
-  </si>
-  <si>
-    <t>佳禾信息有限公司</t>
   </si>
   <si>
     <t>热爱游</t>
@@ -364,9 +346,6 @@
 	266490</t>
   </si>
   <si>
-    <t>凌云科技有限公司</t>
-  </si>
-  <si>
     <t>枫叶</t>
   </si>
   <si>
@@ -387,9 +366,6 @@
 		9407</t>
   </si>
   <si>
-    <t>菊风公司信息有限公司</t>
-  </si>
-  <si>
     <t>诚辉</t>
   </si>
   <si>
@@ -431,9 +407,6 @@
 3156862075	329.4
 	-6
 2553</t>
-  </si>
-  <si>
-    <t>巨奥传媒有限公司</t>
   </si>
   <si>
     <t>答案</t>
@@ -487,9 +460,6 @@
 	1463690</t>
   </si>
   <si>
-    <t>公子(11).xlsx</t>
-  </si>
-  <si>
     <t>14616.6</t>
   </si>
   <si>
@@ -513,9 +483,6 @@
 		725755</t>
   </si>
   <si>
-    <t>思优网络有限公司</t>
-  </si>
-  <si>
     <t>破晓</t>
   </si>
   <si>
@@ -531,9 +498,6 @@
     <t>18726980344</t>
   </si>
   <si>
-    <t>赵斌</t>
-  </si>
-  <si>
     <t>安心游</t>
   </si>
   <si>
@@ -547,9 +511,6 @@
   </si>
   <si>
     <t>13451988118</t>
-  </si>
-  <si>
-    <t>富罳信息有限公司</t>
   </si>
   <si>
     <t>龙琴</t>
@@ -571,9 +532,6 @@
 3654427997	135
 	-6
 	335633</t>
-  </si>
-  <si>
-    <t>侯燕</t>
   </si>
   <si>
     <t>3386.8</t>
@@ -632,9 +590,6 @@
 合计		24626371</t>
   </si>
   <si>
-    <t>合联电子信息有限公司</t>
-  </si>
-  <si>
     <t>拾玖</t>
   </si>
   <si>
@@ -654,9 +609,6 @@
 2105</t>
   </si>
   <si>
-    <t>快讯信息有限公司</t>
-  </si>
-  <si>
     <t>0:17:28</t>
   </si>
   <si>
@@ -673,9 +625,6 @@
 7987</t>
   </si>
   <si>
-    <t>太极传媒有限公司</t>
-  </si>
-  <si>
     <t>0:11:3</t>
   </si>
   <si>
@@ -686,9 +635,6 @@
   </si>
   <si>
     <t>12756058971</t>
-  </si>
-  <si>
-    <t>菠菜(4).xlsx</t>
   </si>
   <si>
     <t>菠菜</t>
@@ -718,9 +664,6 @@
     <t>游戏账号	分销应结
 773174609	359.1
 	359.1</t>
-  </si>
-  <si>
-    <t>四通科技有限公司</t>
   </si>
   <si>
     <t>霸主</t>
@@ -746,9 +689,6 @@
 	258512</t>
   </si>
   <si>
-    <t>浦华众城传媒有限公司</t>
-  </si>
-  <si>
     <t>颜柒</t>
   </si>
   <si>
@@ -768,9 +708,6 @@
 2133468077		1159.2
 1319182480		529.2
 	合计	6491</t>
-  </si>
-  <si>
-    <t>亿游号(11).xlsx</t>
   </si>
   <si>
     <t>潘欢</t>
@@ -837,9 +774,6 @@
 	775503</t>
   </si>
   <si>
-    <t>时刻信息有限公司</t>
-  </si>
-  <si>
     <t>12135.5</t>
   </si>
   <si>
@@ -866,9 +800,6 @@
 	7084</t>
   </si>
   <si>
-    <t>刘斌</t>
-  </si>
-  <si>
     <t>九九</t>
   </si>
   <si>
@@ -894,9 +825,6 @@
 	319953</t>
   </si>
   <si>
-    <t>通际名联科技有限公司</t>
-  </si>
-  <si>
     <t>3194.3</t>
   </si>
   <si>
@@ -917,9 +845,6 @@
 		98118</t>
   </si>
   <si>
-    <t>快讯传媒有限公司</t>
-  </si>
-  <si>
     <t>寻梦游</t>
   </si>
   <si>
@@ -964,9 +889,6 @@
 892763068		599.4
 2465752868		475.2
 		731013</t>
-  </si>
-  <si>
-    <t>超艺科技有限公司</t>
   </si>
   <si>
     <t>淘气游</t>
@@ -1334,11 +1256,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="38.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1357,908 +1281,824 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
       <c r="F2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" t="s">
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" hidden="1">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" hidden="1">
-      <c r="A5" t="s">
+      <c r="D5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B6" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" hidden="1">
-      <c r="A6" t="s">
+      <c r="D6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="s">
+      <c r="B7" t="s">
         <v>33</v>
       </c>
-      <c r="F6" t="s">
+      <c r="C7" t="s">
         <v>34</v>
       </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" hidden="1">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
         <v>35</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>37</v>
       </c>
-      <c r="D7" t="s">
+      <c r="B8" t="s">
         <v>38</v>
       </c>
-      <c r="E7" t="s">
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="F7" t="s">
+      <c r="D8" t="s">
         <v>40</v>
       </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" hidden="1">
-      <c r="A8" t="s">
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>41</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" t="s">
         <v>43</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>44</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>45</v>
       </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" hidden="1">
-      <c r="A9" t="s">
+      <c r="B10" t="s">
         <v>46</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
         <v>47</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10" t="s">
         <v>49</v>
       </c>
-      <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" hidden="1">
-      <c r="A10" t="s">
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>50</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>52</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>53</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>55</v>
       </c>
-      <c r="G10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" hidden="1">
-      <c r="A11" t="s">
+      <c r="B12" t="s">
         <v>56</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C12" t="s">
         <v>57</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>58</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>59</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>60</v>
       </c>
-      <c r="G11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" hidden="1">
-      <c r="A12" t="s">
+      <c r="B13" t="s">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C13" t="s">
         <v>62</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>63</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>64</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>65</v>
       </c>
-      <c r="G12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" hidden="1">
-      <c r="A13" t="s">
+      <c r="B14" t="s">
         <v>66</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C14" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>68</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>69</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
         <v>70</v>
       </c>
-      <c r="G13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" hidden="1">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
         <v>71</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C15" t="s">
         <v>72</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D15" t="s">
         <v>73</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E15" t="s">
         <v>74</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
         <v>75</v>
       </c>
-      <c r="F14" t="s">
+      <c r="B16" t="s">
         <v>76</v>
       </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" hidden="1">
-      <c r="A15" t="s">
+      <c r="C16" t="s">
         <v>77</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D16" t="s">
         <v>78</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E16" t="s">
         <v>79</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
         <v>80</v>
       </c>
-      <c r="E15" t="s">
+      <c r="B17" t="s">
         <v>81</v>
       </c>
-      <c r="F15" t="s">
+      <c r="C17" t="s">
         <v>82</v>
       </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" hidden="1">
-      <c r="A16" t="s">
+      <c r="D17" t="s">
         <v>83</v>
       </c>
-      <c r="B16" t="s">
+      <c r="E17" t="s">
         <v>84</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
         <v>85</v>
       </c>
-      <c r="D16" t="s">
+      <c r="B18" t="s">
         <v>86</v>
       </c>
-      <c r="E16" t="s">
+      <c r="C18" t="s">
         <v>87</v>
       </c>
-      <c r="F16" t="s">
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
         <v>88</v>
       </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" hidden="1">
-      <c r="A17" t="s">
+      <c r="B19" t="s">
         <v>89</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C19" t="s">
         <v>90</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" t="s">
         <v>91</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
         <v>92</v>
       </c>
-      <c r="F17" t="s">
+      <c r="B20" t="s">
         <v>93</v>
       </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" hidden="1">
-      <c r="A18" t="s">
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
         <v>94</v>
       </c>
-      <c r="B18" t="s">
+      <c r="E20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
         <v>95</v>
       </c>
-      <c r="D18" t="s">
+      <c r="B21" t="s">
         <v>96</v>
       </c>
-      <c r="E18" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" hidden="1">
-      <c r="A19" t="s">
+      <c r="C21" t="s">
         <v>97</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D21" t="s">
         <v>98</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E21" t="s">
         <v>99</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
         <v>100</v>
       </c>
-      <c r="E19" t="s">
+      <c r="B22" t="s">
         <v>101</v>
       </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" hidden="1">
-      <c r="A20" t="s">
+      <c r="C22" t="s">
         <v>102</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D22" t="s">
         <v>103</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E22" t="s">
         <v>104</v>
       </c>
-      <c r="D20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
         <v>105</v>
       </c>
-      <c r="F20" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" hidden="1">
-      <c r="A21" t="s">
+      <c r="B23" t="s">
         <v>106</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C23" t="s">
         <v>107</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D23" t="s">
         <v>108</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E23" t="s">
         <v>109</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
         <v>110</v>
       </c>
-      <c r="F21" t="s">
+      <c r="B24" t="s">
         <v>111</v>
       </c>
-      <c r="G21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" hidden="1">
-      <c r="A22" t="s">
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" t="s">
         <v>112</v>
       </c>
-      <c r="B22" t="s">
+      <c r="E24" t="s">
         <v>113</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
         <v>114</v>
       </c>
-      <c r="D22" t="s">
+      <c r="B25" t="s">
         <v>115</v>
       </c>
-      <c r="E22" t="s">
+      <c r="C25" t="s">
         <v>116</v>
       </c>
-      <c r="F22" t="s">
+      <c r="D25" t="s">
         <v>117</v>
       </c>
-      <c r="G22" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" hidden="1">
-      <c r="A23" t="s">
+      <c r="E25" t="s">
         <v>118</v>
       </c>
-      <c r="B23" t="s">
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
         <v>119</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B26" t="s">
         <v>120</v>
       </c>
-      <c r="D23" t="s">
+      <c r="C26" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s">
         <v>121</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F26" t="s">
         <v>122</v>
       </c>
-      <c r="F23" t="s">
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
         <v>123</v>
       </c>
-      <c r="G23" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" hidden="1">
-      <c r="A24" t="s">
+      <c r="B27" t="s">
         <v>124</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" t="s">
         <v>125</v>
       </c>
-      <c r="C24" t="s">
+      <c r="F27" t="s">
         <v>126</v>
       </c>
-      <c r="D24" t="s">
-        <v>96</v>
-      </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
         <v>127</v>
       </c>
-      <c r="F24" t="s">
+      <c r="B28" t="s">
         <v>128</v>
       </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" hidden="1">
-      <c r="A25" t="s">
+      <c r="C28" t="s">
         <v>129</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D28" t="s">
         <v>130</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E28" t="s">
         <v>131</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
         <v>132</v>
       </c>
-      <c r="E25" t="s">
+      <c r="B29" t="s">
         <v>133</v>
       </c>
-      <c r="F25" t="s">
+      <c r="C29" t="s">
         <v>134</v>
       </c>
-      <c r="G25" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" hidden="1">
-      <c r="A26" t="s">
+      <c r="D29" t="s">
         <v>135</v>
       </c>
-      <c r="B26" t="s">
+      <c r="E29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
         <v>136</v>
       </c>
-      <c r="C26" t="s">
+      <c r="B30" t="s">
         <v>137</v>
       </c>
-      <c r="D26" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" t="s">
-        <v>101</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="C30" t="s">
         <v>138</v>
       </c>
-      <c r="G26" t="s">
+      <c r="D30" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" hidden="1">
-      <c r="A27" t="s">
+      <c r="E30" t="s">
         <v>140</v>
       </c>
-      <c r="B27" t="s">
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
         <v>141</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B31" t="s">
         <v>142</v>
       </c>
-      <c r="D27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" t="s">
-        <v>101</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="C31" t="s">
         <v>143</v>
       </c>
-      <c r="G27" t="s">
+      <c r="D31" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" hidden="1">
-      <c r="A28" t="s">
+      <c r="E31" t="s">
         <v>145</v>
       </c>
-      <c r="B28" t="s">
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
         <v>146</v>
       </c>
-      <c r="C28" t="s">
+      <c r="B32" t="s">
         <v>147</v>
       </c>
-      <c r="D28" t="s">
+      <c r="C32" t="s">
         <v>148</v>
       </c>
-      <c r="E28" t="s">
+      <c r="D32" t="s">
         <v>149</v>
       </c>
-      <c r="F28" t="s">
+      <c r="E32" t="s">
         <v>150</v>
       </c>
-      <c r="G28" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" hidden="1">
-      <c r="A29" t="s">
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
         <v>151</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B33" t="s">
         <v>152</v>
       </c>
-      <c r="D29" t="s">
+      <c r="C33" t="s">
         <v>153</v>
       </c>
-      <c r="E29" t="s">
+      <c r="D33" t="s">
         <v>154</v>
       </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-      <c r="G29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" hidden="1">
-      <c r="A30" t="s">
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
         <v>155</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B34" t="s">
         <v>156</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" t="s">
         <v>157</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E34" t="s">
         <v>158</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
         <v>159</v>
       </c>
-      <c r="F30" t="s">
+      <c r="B35" t="s">
         <v>160</v>
       </c>
-      <c r="G30" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" hidden="1">
-      <c r="A31" t="s">
+      <c r="C35" t="s">
         <v>161</v>
       </c>
-      <c r="B31" t="s">
+      <c r="D35" t="s">
         <v>162</v>
       </c>
-      <c r="C31" t="s">
+      <c r="E35" t="s">
         <v>163</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
         <v>164</v>
       </c>
-      <c r="E31" t="s">
+      <c r="B36" t="s">
         <v>165</v>
       </c>
-      <c r="F31" t="s">
+      <c r="C36" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" t="s">
         <v>166</v>
       </c>
-      <c r="G31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" hidden="1">
-      <c r="A32" t="s">
+      <c r="E36" t="s">
         <v>167</v>
       </c>
-      <c r="B32" t="s">
+      <c r="F36" t="s">
         <v>168</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
         <v>169</v>
       </c>
-      <c r="D32" t="s">
+      <c r="B37" t="s">
         <v>170</v>
       </c>
-      <c r="E32" t="s">
+      <c r="C37" t="s">
         <v>171</v>
       </c>
-      <c r="F32" t="s">
+      <c r="D37" t="s">
         <v>172</v>
       </c>
-      <c r="G32" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" hidden="1">
-      <c r="A33" t="s">
+      <c r="E37" t="s">
         <v>173</v>
       </c>
-      <c r="B33" t="s">
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
         <v>174</v>
       </c>
-      <c r="C33" t="s">
-        <v>163</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="B38" t="s">
         <v>175</v>
       </c>
-      <c r="E33" t="s">
+      <c r="C38" t="s">
         <v>176</v>
       </c>
-      <c r="F33" t="s">
-        <v>18</v>
-      </c>
-      <c r="G33" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" t="s">
+      <c r="D38" t="s">
         <v>177</v>
       </c>
-      <c r="B34" t="s">
+      <c r="E38" t="s">
         <v>178</v>
       </c>
-      <c r="C34" t="s">
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
         <v>179</v>
       </c>
-      <c r="D34" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="B39" t="s">
         <v>180</v>
       </c>
-      <c r="F34" t="s">
+      <c r="C39" t="s">
         <v>181</v>
       </c>
-      <c r="G34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" hidden="1">
-      <c r="A35" t="s">
+      <c r="D39" t="s">
         <v>182</v>
       </c>
-      <c r="B35" t="s">
+      <c r="E39" t="s">
+        <v>69</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
         <v>183</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B40" t="s">
         <v>184</v>
       </c>
-      <c r="D35" t="s">
+      <c r="C40" t="s">
         <v>185</v>
       </c>
-      <c r="E35" t="s">
+      <c r="D40" t="s">
         <v>186</v>
       </c>
-      <c r="F35" t="s">
+      <c r="E40" t="s">
         <v>187</v>
       </c>
-      <c r="G35" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" hidden="1">
-      <c r="A36" t="s">
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
         <v>188</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B41" t="s">
         <v>189</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C41" t="s">
         <v>190</v>
       </c>
-      <c r="D36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="D41" t="s">
         <v>191</v>
       </c>
-      <c r="F36" t="s">
-        <v>192</v>
-      </c>
-      <c r="G36" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" hidden="1">
-      <c r="A37" t="s">
-        <v>194</v>
-      </c>
-      <c r="B37" t="s">
-        <v>195</v>
-      </c>
-      <c r="C37" t="s">
-        <v>196</v>
-      </c>
-      <c r="D37" t="s">
-        <v>197</v>
-      </c>
-      <c r="E37" t="s">
-        <v>198</v>
-      </c>
-      <c r="F37" t="s">
-        <v>199</v>
-      </c>
-      <c r="G37" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" hidden="1">
-      <c r="A38" t="s">
-        <v>200</v>
-      </c>
-      <c r="B38" t="s">
-        <v>201</v>
-      </c>
-      <c r="D38" t="s">
-        <v>202</v>
-      </c>
-      <c r="E38" t="s">
-        <v>203</v>
-      </c>
-      <c r="F38" t="s">
-        <v>204</v>
-      </c>
-      <c r="G38" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" hidden="1">
-      <c r="A39" t="s">
-        <v>205</v>
-      </c>
-      <c r="B39" t="s">
-        <v>206</v>
-      </c>
-      <c r="D39" t="s">
-        <v>207</v>
-      </c>
-      <c r="E39" t="s">
-        <v>208</v>
-      </c>
-      <c r="F39" t="s">
-        <v>76</v>
-      </c>
-      <c r="G39" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" hidden="1">
-      <c r="A40" t="s">
-        <v>209</v>
-      </c>
-      <c r="B40" t="s">
-        <v>210</v>
-      </c>
-      <c r="C40" t="s">
-        <v>211</v>
-      </c>
-      <c r="D40" t="s">
-        <v>212</v>
-      </c>
-      <c r="E40" t="s">
-        <v>213</v>
-      </c>
-      <c r="F40" t="s">
-        <v>214</v>
-      </c>
-      <c r="G40" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" hidden="1">
-      <c r="A41" t="s">
-        <v>215</v>
-      </c>
-      <c r="B41" t="s">
-        <v>216</v>
-      </c>
-      <c r="C41" t="s">
-        <v>79</v>
-      </c>
-      <c r="D41" t="s">
-        <v>217</v>
-      </c>
       <c r="E41" t="s">
-        <v>218</v>
+        <v>21</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G41" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="yc"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:F41" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x01010028C7B6C620067247A35EF62A3E68EE62" ma:contentTypeVersion="2" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="afb9c51b290a08b96651a149e23bf63d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5c256d110dbc588a3a1a6b419ffcea87" ns2:_="">
     <xsd:import namespace="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7"/>
@@ -2406,15 +2246,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2422,11 +2253,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81CD8683-80AD-45C4-8D21-18D3E96193C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE5AEDA-CC25-40D6-B73B-C7413BD2B9D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE5AEDA-CC25-40D6-B73B-C7413BD2B9D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81CD8683-80AD-45C4-8D21-18D3E96193C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
